--- a/methods/material/prio.xlsx
+++ b/methods/material/prio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\EFSPI\10_efspi_europe\methods\material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677451C7-85F1-47AD-9B4E-48B5DF703C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCD4B16-20DC-4327-BBE0-8E2E306A61A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3070" yWindow="3830" windowWidth="22240" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>Priority topic</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Comment</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Covariate adjustment</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>These topics are aligned with both EFSPI and EFPIA and input from further stakeholders, e.g. the EFSPI / PSI SIGs, is sought as well. The idea is to be prepared for discussions with regulators once there are opportunities, e.g. within EMA multistakeholder workshops.</t>
-  </si>
-  <si>
     <t>material/Charter_Bayes.pdf</t>
   </si>
   <si>
@@ -73,6 +67,33 @@
   </si>
   <si>
     <t>Mike Krams, Nicky Best</t>
+  </si>
+  <si>
+    <t>To be confirmed</t>
+  </si>
+  <si>
+    <t>material/Charter_CovariateAdj.pdf</t>
+  </si>
+  <si>
+    <t>material/Charter_Credibility.pdf</t>
+  </si>
+  <si>
+    <t>material/Charter_Estimands.pdf</t>
+  </si>
+  <si>
+    <t>material/Charter_AI.pdf</t>
+  </si>
+  <si>
+    <t>Alex Ocampo</t>
+  </si>
+  <si>
+    <t>Tobias Mielke</t>
+  </si>
+  <si>
+    <t>David Wright</t>
+  </si>
+  <si>
+    <t>Marc Vandemeulebroecke</t>
   </si>
 </sst>
 </file>
@@ -393,12 +414,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="60.90625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.7265625" style="1"/>
@@ -415,7 +436,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -423,50 +444,72 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>4</v>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
